--- a/output/laminas_comunales/comunal_s_isapre_a_2023_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2023_los_lagos.xlsx
@@ -375,211 +375,211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C2">
-        <v>31521</v>
+        <v>25.47576972745191</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C3">
-        <v>19678</v>
+        <v>11.4929587862904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="C4">
-        <v>14993</v>
+        <v>11.35773198476556</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C5">
-        <v>6227</v>
+        <v>11.09300922820211</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="C6">
-        <v>3096</v>
+        <v>10.3085495675316</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C7">
-        <v>2479</v>
+        <v>9.401002384312198</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="C8">
-        <v>1932</v>
+        <v>8.01568536993253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="C9">
-        <v>1725</v>
+        <v>7.669831994156318</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="C10">
-        <v>1390</v>
+        <v>6.463600492703397</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="C11">
-        <v>1203</v>
+        <v>6.077995081391264</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="C12">
-        <v>934</v>
+        <v>5.944197331176708</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="C13">
-        <v>901</v>
+        <v>5.361971962326319</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="C14">
-        <v>843</v>
+        <v>5.259164137286948</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="C15">
-        <v>718</v>
+        <v>5.054562897229884</v>
       </c>
     </row>
     <row r="16">
@@ -594,82 +594,82 @@
         </is>
       </c>
       <c r="C16">
-        <v>648</v>
+        <v>4.897959183673469</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C17">
-        <v>612</v>
+        <v>4.860123281175913</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="C18">
-        <v>588</v>
+        <v>4.837742957444987</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="C19">
-        <v>565</v>
+        <v>4.802675585284281</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="C20">
-        <v>519</v>
+        <v>4.588815789473684</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="C21">
-        <v>517</v>
+        <v>4.352283317800559</v>
       </c>
     </row>
     <row r="22">
@@ -684,112 +684,112 @@
         </is>
       </c>
       <c r="C22">
-        <v>504</v>
+        <v>3.704520396912899</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C23">
-        <v>315</v>
+        <v>3.517889266440136</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="C24">
-        <v>288</v>
+        <v>3.20855614973262</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="C25">
-        <v>279</v>
+        <v>3.171390013495277</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="C26">
-        <v>205</v>
+        <v>3.122966818477554</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="C27">
-        <v>176</v>
+        <v>3.113332530410695</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C28">
-        <v>141</v>
+        <v>3.110134436401241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="C29">
-        <v>116</v>
+        <v>2.941176470588236</v>
       </c>
     </row>
     <row r="30">
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="C30">
-        <v>88</v>
+        <v>2.71521135452021</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="C31">
-        <v>76</v>
+        <v>1.358472889097084</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
